--- a/backend/Pre-process/Product_Normalizer2.0/Spec_words/spec_words_dict.xlsx
+++ b/backend/Pre-process/Product_Normalizer2.0/Spec_words/spec_words_dict.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19180" windowHeight="8060"/>
+    <workbookView windowWidth="19200" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1838,7 +1838,7 @@
     <t>黄豆酱</t>
   </si>
   <si>
-    <t>蓝莓果酱</t>
+    <t>果酱</t>
   </si>
   <si>
     <t>蒜蓉辣酱</t>
